--- a/Data/Masterlist_FOUN_courses_by_quarter.xlsx
+++ b/Data/Masterlist_FOUN_courses_by_quarter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmadrid/Library/Mobile Documents/com~apple~CloudDocs/Desktop/Scheduling/Docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmadrid/Projects/forecast-tool/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8891A580-F318-7346-82B7-15B65A755CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2117B40A-9242-5F42-9D23-5EC6185D9458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FOUN Mapped Quarters" sheetId="1" r:id="rId1"/>
@@ -633,7 +633,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.1640625" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="2" max="2" width="47" customWidth="1"/>
     <col min="3" max="3" width="67.6640625" customWidth="1"/>
     <col min="4" max="4" width="29.5" customWidth="1"/>
     <col min="5" max="5" width="42.6640625" customWidth="1"/>
